--- a/ComcastCRMGUIFrameworkk/testdata/testScriptdata.xlsx
+++ b/ComcastCRMGUIFrameworkk/testdata/testScriptdata.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{4468F7B7-D327-448C-B106-EFB572B3BB91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{DC0E9E9C-FDC7-4845-B1AD-9EC471F201A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{6C80BAAA-37DD-4FF9-A0B6-63EFABFF3705}"/>
   </bookViews>
@@ -13,7 +13,7 @@
     <sheet name="contact" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
-  <oleSize ref="A1:K13"/>
+  <oleSize ref="A1:K19"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="66">
   <si>
     <t>Test case name</t>
   </si>
@@ -212,6 +212,12 @@
   </si>
   <si>
     <t>Deepak_</t>
+  </si>
+  <si>
+    <t>PASS</t>
+  </si>
+  <si>
+    <t>9876543210</t>
   </si>
   <si>
     <t>FaceBook_</t>
@@ -259,12 +265,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -831,6 +838,9 @@
       <c r="C1" t="s">
         <v>37</v>
       </c>
+      <c r="E1" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
@@ -842,6 +852,9 @@
       <c r="C2" t="s">
         <v>40</v>
       </c>
+      <c r="E2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
@@ -901,8 +914,8 @@
       <c r="C8" t="s">
         <v>58</v>
       </c>
-      <c r="D8">
-        <v>9999999999</v>
+      <c r="D8" s="3" t="s">
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -996,7 +1009,10 @@
         <v>55</v>
       </c>
       <c r="C8" t="s">
-        <v>63</v>
+        <v>65</v>
+      </c>
+      <c r="D8" t="s">
+        <v>62</v>
       </c>
     </row>
   </sheetData>
